--- a/Results/Ammonia/ammonia climate change remind breakdown results.xlsx
+++ b/Results/Ammonia/ammonia climate change remind breakdown results.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,55 +454,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tap water production, conventional treatment</t>
+          <t>heat production, natural gas, at industrial furnace &gt;100kW</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>market group for electricity, high voltage</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>market for solvent, organic</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>market for chemical factory, organics</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>catalysts for ammonia synthesis from SMR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>carbon dioxide MEA capture, without energy consumption and flue gas emissions</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>activated carbon production, granular from hard coal</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>natural gas burnt in furnace excluding carbon dioxide generated in flue gas</t>
+          <t>market for municipal solid waste</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>market group for electricity, high voltage</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of inert waste, inert material landfill</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of wastewater, average, capacity 1E9l/year</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>direct emissions</t>
         </is>
@@ -523,43 +508,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.216529554116152</v>
+        <v>2.742852760949717</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3062635006088573</v>
+        <v>0.2549243901051878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002190737650535615</v>
+        <v>0.9829935092765117</v>
       </c>
       <c r="G2" t="n">
-        <v>3.761551377937929e-06</v>
+        <v>0.02007413640205909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04504922997104636</v>
+        <v>0.006604430142347567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001071876306356467</v>
+        <v>0.000580806718677014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0109318671201239</v>
+        <v>2.302070441761118e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0006769952719000832</v>
+        <v>0.04481724723661824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002352325092302141</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3812422313926973</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.816754658957575e-06</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0001027821712842771</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.467340443752937</v>
+        <v>1.432599987854667</v>
       </c>
     </row>
     <row r="3">
@@ -577,43 +553,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.077934394918358</v>
+        <v>2.725303214842976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3061708987510517</v>
+        <v>0.2548473111451526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001573019155140558</v>
+        <v>0.979628297876614</v>
       </c>
       <c r="G3" t="n">
-        <v>3.277373176466138e-06</v>
+        <v>0.01317239671303641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03817035925828288</v>
+        <v>0.006380735230671422</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009512337568409115</v>
+        <v>0.0004430777559259851</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01055003113265285</v>
+        <v>2.238691079754908e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0006522230671353622</v>
+        <v>0.03797379953194509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002352214795352527</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2501663740390214</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.872720296947626e-06</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9.485970037827658e-05</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.467340443344618</v>
+        <v>1.432599988199297</v>
       </c>
     </row>
     <row r="4">
@@ -631,43 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.983557847762921</v>
+        <v>2.717002119291374</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3093046000025833</v>
+        <v>0.2574557084198207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001136251190786207</v>
+        <v>0.9786834285538921</v>
       </c>
       <c r="G4" t="n">
-        <v>2.920218644169507e-06</v>
+        <v>0.008317747207024133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0332564816432999</v>
+        <v>0.00625719952265074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008679271330033211</v>
+        <v>0.0003457550814451456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01026773209747286</v>
+        <v>2.188573879581109e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0006351844664722606</v>
+        <v>0.03308522611786629</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002351803343958302</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1579682653267713</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.981826079029613e-06</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8.908990171268327e-05</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.467340442967088</v>
+        <v>1.432599988315483</v>
       </c>
     </row>
     <row r="5">
@@ -685,43 +643,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.051809296826287</v>
+        <v>2.706568639069444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2928862449178877</v>
+        <v>0.2437895707698048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001508224244854057</v>
+        <v>0.9740429424991267</v>
       </c>
       <c r="G5" t="n">
-        <v>3.18677518559115e-06</v>
+        <v>0.01257632262447243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03676216403655429</v>
+        <v>0.006301838417214081</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009284763639056878</v>
+        <v>0.0004281652402913289</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01046533392123889</v>
+        <v>2.188722295844691e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0006481168103318547</v>
+        <v>0.03657285586542295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002350676801236709</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2388459061968175</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.655081344133511e-06</v>
-      </c>
-      <c r="O5" t="n">
-        <v>9.32142522781946e-05</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.467340443673262</v>
+        <v>1.43259998875003</v>
       </c>
     </row>
     <row r="6">
@@ -739,43 +688,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.842258094813199</v>
+        <v>2.670441816574735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2825425226335689</v>
+        <v>0.2351797720523432</v>
       </c>
       <c r="F6" t="n">
-        <v>6.020480534601399e-05</v>
+        <v>0.9663529060901465</v>
       </c>
       <c r="G6" t="n">
-        <v>2.456644873147245e-06</v>
+        <v>0.002609191540530294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02760273738649432</v>
+        <v>0.005761063597525462</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007441499586685893</v>
+        <v>0.0002229432388318135</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009961002558965633</v>
+        <v>2.053637100285325e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0006099185979134048</v>
+        <v>0.02746059603356254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.00023481804724801</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04955301613576177</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.459090236606461e-06</v>
-      </c>
-      <c r="O6" t="n">
-        <v>8.00548245588686e-05</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.467340443378979</v>
+        <v>1.432599989603544</v>
       </c>
     </row>
     <row r="7">
@@ -793,43 +733,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.80499333830527</v>
+        <v>2.659524488409336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2783829346544844</v>
+        <v>0.2317174579778651</v>
       </c>
       <c r="F7" t="n">
-        <v>4.330414934207707e-05</v>
+        <v>0.9641935535072839</v>
       </c>
       <c r="G7" t="n">
-        <v>2.230490699121056e-06</v>
+        <v>0.001050066925243466</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02432073023083695</v>
+        <v>0.005338925383329605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006926439141321503</v>
+        <v>0.0001753335278144404</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009813700648322345</v>
+        <v>1.928929448185281e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0006009787735761627</v>
+        <v>0.02419548969940352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002343822445110979</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01994256936753793</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.009917260502553e-06</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7.478433036728954e-05</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.467340443382203</v>
+        <v>1.432599989849403</v>
       </c>
     </row>
     <row r="8">
@@ -847,43 +778,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.904883083040554</v>
+        <v>2.674253781160294</v>
       </c>
       <c r="E8" t="n">
-        <v>0.276813119379838</v>
+        <v>0.2304107916572901</v>
       </c>
       <c r="F8" t="n">
-        <v>9.178057341769646e-05</v>
+        <v>0.967758829591565</v>
       </c>
       <c r="G8" t="n">
-        <v>2.731300324335517e-06</v>
+        <v>0.006009646307155857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0311043694683473</v>
+        <v>0.005977601838386653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008104314372245386</v>
+        <v>0.0002965216232766402</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01014320009519206</v>
+        <v>2.120614075920208e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0006235021795827518</v>
+        <v>0.03094419632695144</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002349980674677673</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1141334761372828</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.583426876012356e-06</v>
-      </c>
-      <c r="O8" t="n">
-        <v>8.548366392989633e-05</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.467340443744045</v>
+        <v>1.432599989607441</v>
       </c>
     </row>
     <row r="9">
@@ -901,43 +823,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.769764336322213</v>
+        <v>2.624396549169136</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2496990478344541</v>
+        <v>0.2078418660809996</v>
       </c>
       <c r="F9" t="n">
-        <v>4.089266597089253e-05</v>
+        <v>0.9532771809726606</v>
       </c>
       <c r="G9" t="n">
-        <v>2.226679726700344e-06</v>
+        <v>0.0007088224816535315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02428055683940917</v>
+        <v>0.005389317962532587</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006892879184809668</v>
+        <v>0.000169804045387021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009794154150281585</v>
+        <v>1.95516540948669e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0006002028128604651</v>
+        <v>0.02415552318239289</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002344918326662287</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01346175293195624</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.126573222557677e-06</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7.508337638315663e-05</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.467340444171528</v>
+        <v>1.432599990956749</v>
       </c>
     </row>
     <row r="10">
@@ -955,43 +868,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.758628358034176</v>
+        <v>2.595619021271621</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2472817642819473</v>
+        <v>0.2058297930324351</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3918229241006e-05</v>
+        <v>0.9303570490019334</v>
       </c>
       <c r="G10" t="n">
-        <v>2.030992527849657e-06</v>
+        <v>0.0004198553024886839</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02122495211917895</v>
+        <v>0.004906348575617324</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006497559835727979</v>
+        <v>0.0001385799366023206</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009664608026110822</v>
+        <v>1.788546422498255e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0005930262038060104</v>
+        <v>0.02111565341565224</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002338649298330928</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007973771283452275</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.91993660997011e-07</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.978114515053442e-05</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.46734044418948</v>
+        <v>1.432599991612834</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,60 +935,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tap water production, conventional treatment</t>
+          <t>natural gas heating, with CCS</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>market group for electricity, high voltage</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>market for solvent, organic</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>market for chemical factory, organics</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>catalysts for ammonia synthesis from SMR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>carbon dioxide MEA capture, without energy consumption and flue gas emissions</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carbon dioxide transport and injection in a geological resovoir</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>natural gas burnt in furnace excluding carbon dioxide generated in flue gas</t>
+          <t>market for municipal solid waste</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>electricity with CCS, high voltage</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>heat with CCS</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of inert waste, inert material landfill</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of wastewater, average, capacity 1E9l/year</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>direct emissions</t>
         </is>
@@ -1105,46 +989,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5714561142980832</v>
+        <v>1.990557743927718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3062635006088573</v>
+        <v>0.2549243901051878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002190737650535615</v>
+        <v>0.3743660563077815</v>
       </c>
       <c r="G2" t="n">
-        <v>3.761551377937929e-06</v>
+        <v>0.02007413640205909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04504922997104636</v>
+        <v>0.006604430142347567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001071876306356467</v>
+        <v>0.000580806718677014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01317430140117499</v>
+        <v>2.302070441761118e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0141329796049708</v>
+        <v>0.04481724723661824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002352325092302141</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1030946161537607</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.02319451566490417</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.816754658957575e-06</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.0001027821712842771</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.06016769435097802</v>
+        <v>1.288932423801399</v>
       </c>
     </row>
     <row r="3">
@@ -1162,46 +1034,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4119753385319539</v>
+        <v>1.933852614785587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3061708987510517</v>
+        <v>0.2548473111451526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001573019155140558</v>
+        <v>0.331845260930385</v>
       </c>
       <c r="G3" t="n">
-        <v>3.277373176466138e-06</v>
+        <v>0.01317239671303641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03817035925828288</v>
+        <v>0.006380735230671422</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009512337568409115</v>
+        <v>0.0004430777559259851</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01271414008294064</v>
+        <v>2.238691079754908e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01141317677812182</v>
+        <v>0.03797379953194509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002352214795352527</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04417011031519789</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.02132067253945681</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.872720296947626e-06</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9.485970037827658e-05</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.06016768997743166</v>
+        <v>1.288932425088137</v>
       </c>
     </row>
     <row r="4">
@@ -1219,46 +1079,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3035173380064015</v>
+        <v>1.898315518402883</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3093046000025833</v>
+        <v>0.2574557084198207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001136251190786207</v>
+        <v>0.3036643901212501</v>
       </c>
       <c r="G4" t="n">
-        <v>2.920218644169507e-06</v>
+        <v>0.008317747207024133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0332564816432999</v>
+        <v>0.00625719952265074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008679271330033211</v>
+        <v>0.0003457550814451456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01237393355336475</v>
+        <v>2.188573879581109e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009724241586578756</v>
+        <v>0.03308522611786629</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002351803343958302</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1475031563712131</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0201380405855281</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.981826079029613e-06</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8.908990171268327e-05</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.06016768681408236</v>
+        <v>1.288932425859635</v>
       </c>
     </row>
     <row r="5">
@@ -1276,46 +1124,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3822760811126097</v>
+        <v>1.909829097870338</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2928862449178877</v>
+        <v>0.2437895707698048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001508224244854057</v>
+        <v>0.3209709642839296</v>
       </c>
       <c r="G5" t="n">
-        <v>3.18677518559115e-06</v>
+        <v>0.01257632262447243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03676216403655429</v>
+        <v>0.006301838417214081</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009284763639056878</v>
+        <v>0.0004281652402913289</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01261206908456995</v>
+        <v>2.188722295844691e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01075739270019615</v>
+        <v>0.03657285586542295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002350676801236709</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05773561393516947</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.0206688134741377</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.655081344133511e-06</v>
-      </c>
-      <c r="P5" t="n">
-        <v>9.32142522781946e-05</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.06016768994357463</v>
+        <v>1.288932425766121</v>
       </c>
     </row>
     <row r="6">
@@ -1333,46 +1169,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1410783398748049</v>
+        <v>1.814452288503936</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2825425226335689</v>
+        <v>0.2351797720523432</v>
       </c>
       <c r="F6" t="n">
-        <v>6.020480534601399e-05</v>
+        <v>0.2540309395776655</v>
       </c>
       <c r="G6" t="n">
-        <v>2.456644873147245e-06</v>
+        <v>0.002609191540530294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02760273738649432</v>
+        <v>0.005761063597525462</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007441499586685893</v>
+        <v>0.0002229432388318135</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0120042851351637</v>
+        <v>2.053637100285325e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006176389353419801</v>
+        <v>0.02746059603356254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.00023481804724801</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2709678547170126</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.01768428484616557</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.459090236606461e-06</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8.00548245588686e-05</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.06016768391966226</v>
+        <v>1.288932428045226</v>
       </c>
     </row>
     <row r="7">
@@ -1390,46 +1214,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09731859715911893</v>
+        <v>1.79380001095959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2783829346544844</v>
+        <v>0.2317174579778651</v>
       </c>
       <c r="F7" t="n">
-        <v>4.330414934207707e-05</v>
+        <v>0.2421366373816277</v>
       </c>
       <c r="G7" t="n">
-        <v>2.230490699121056e-06</v>
+        <v>0.001050066925243466</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02432073023083695</v>
+        <v>0.005338925383329605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006926439141321503</v>
+        <v>0.0001753335278144404</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01182676744797825</v>
+        <v>1.928929448185281e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004517541935642163</v>
+        <v>0.02419548969940352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002343822445110979</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.304774191218943</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.01708319227979362</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.009917260502553e-06</v>
-      </c>
-      <c r="P7" t="n">
-        <v>7.478433036728954e-05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.06016768303386572</v>
+        <v>1.288932428525313</v>
       </c>
     </row>
     <row r="8">
@@ -1447,46 +1259,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21449940041856</v>
+        <v>1.834692530302356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.276813119379838</v>
+        <v>0.2304107916572901</v>
       </c>
       <c r="F8" t="n">
-        <v>9.178057341769646e-05</v>
+        <v>0.2718651406872118</v>
       </c>
       <c r="G8" t="n">
-        <v>2.731300324335517e-06</v>
+        <v>0.006009646307155857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0311043694683473</v>
+        <v>0.005977601838386653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008104314372245386</v>
+        <v>0.0002965216232766402</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01222385652497504</v>
+        <v>2.120614075920208e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007928690686061576</v>
+        <v>0.03094419632695144</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002349980674677673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.198315364115883</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.01860506584845465</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.583426876012356e-06</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.548366392989633e-05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0601676862313342</v>
+        <v>1.288932427653857</v>
       </c>
     </row>
     <row r="9">
@@ -1504,46 +1304,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05902040081744741</v>
+        <v>1.751954677230468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2496990478344541</v>
+        <v>0.2078418660809996</v>
       </c>
       <c r="F9" t="n">
-        <v>4.089266597089253e-05</v>
+        <v>0.2245028701964585</v>
       </c>
       <c r="G9" t="n">
-        <v>2.226679726700344e-06</v>
+        <v>0.0007088224816535315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02428055683940917</v>
+        <v>0.005389317962532587</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006892879184809668</v>
+        <v>0.000169804045387021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01180321141187779</v>
+        <v>1.95516540948669e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004615627582488286</v>
+        <v>0.02415552318239289</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002344918326662287</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3133890958161482</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.01605478618454</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.126573222557677e-06</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7.508337638315663e-05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.06016768357338219</v>
+        <v>1.288932429794283</v>
       </c>
     </row>
     <row r="10">
@@ -1561,46 +1349,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03966501124471946</v>
+        <v>1.742935743904813</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2472817642819473</v>
+        <v>0.2058297930324351</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3918229241006e-05</v>
+        <v>0.2213413332729941</v>
       </c>
       <c r="G10" t="n">
-        <v>2.030992527849657e-06</v>
+        <v>0.0004198553024886839</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02122495211917895</v>
+        <v>0.004906348575617324</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006497559835727979</v>
+        <v>0.0001385799366023206</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01164709172377457</v>
+        <v>1.788546422498255e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00283639171735939</v>
+        <v>0.02111565341565224</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00497996599365975</v>
+        <v>0.0002338649298330928</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.323110335288367</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.01388161901381667</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.91993660997011e-07</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6.978114515053442e-05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.06016768333919666</v>
+        <v>1.288932429974965</v>
       </c>
     </row>
   </sheetData>
@@ -1684,28 +1460,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6340057313660538</v>
+        <v>0.6340057313660551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002329170541490541</v>
+        <v>0.0002329170541490536</v>
       </c>
       <c r="F2" t="n">
-        <v>8.751891389403391e-05</v>
+        <v>8.751891389403393e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03705299165118561</v>
+        <v>0.03705299165118563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2267066103254961</v>
+        <v>0.2267066103254966</v>
       </c>
       <c r="I2" t="n">
-        <v>3.080097898724995e-07</v>
+        <v>3.080097898724961e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.361488390172494</v>
+        <v>0.3614883901724956</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436995239045175</v>
+        <v>0.008436995239044287</v>
       </c>
     </row>
     <row r="3">
@@ -1723,28 +1499,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5073965993184052</v>
+        <v>0.5073965993184059</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001920294371165649</v>
+        <v>0.0001920294371165651</v>
       </c>
       <c r="F3" t="n">
-        <v>6.638292176127781e-05</v>
+        <v>6.638292176127786e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03139512048993765</v>
+        <v>0.03139512048993768</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1487620363269474</v>
+        <v>0.1487620363269481</v>
       </c>
       <c r="I3" t="n">
-        <v>3.174981180363513e-07</v>
+        <v>3.174981180363519e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3185437162663066</v>
+        <v>0.3185437162663073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436996378217598</v>
+        <v>0.008436996378216877</v>
       </c>
     </row>
     <row r="4">
@@ -1762,28 +1538,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4288648735213336</v>
+        <v>0.4288648735213333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001633145496694449</v>
+        <v>0.0001633145496694451</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117235834304978e-05</v>
+        <v>5.117235834304968e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.02735345615161417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09393620911410068</v>
+        <v>0.09393620911410092</v>
       </c>
       <c r="I4" t="n">
-        <v>3.359957444754823e-07</v>
+        <v>3.359957444755234e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2989233882285831</v>
+        <v>0.2989233882285833</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436997123278667</v>
+        <v>0.008436997123277945</v>
       </c>
     </row>
     <row r="5">
@@ -1801,28 +1577,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5043918025945241</v>
+        <v>0.5043918025945243</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001863807500215076</v>
+        <v>0.0001863807500215082</v>
       </c>
       <c r="F5" t="n">
-        <v>6.369871684704232e-05</v>
+        <v>6.369871684704234e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03023687992006593</v>
+        <v>0.03023687992006594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1420302928828136</v>
+        <v>0.1420302928828134</v>
       </c>
       <c r="I5" t="n">
-        <v>2.805999448053988e-07</v>
+        <v>2.805999448054026e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3234372732824707</v>
+        <v>0.3234372732824713</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436996442360511</v>
+        <v>0.008436996442360289</v>
       </c>
     </row>
     <row r="6">
@@ -1843,25 +1619,25 @@
         <v>0.3244792021989104</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001312469477801923</v>
+        <v>0.0001312469477801922</v>
       </c>
       <c r="F6" t="n">
-        <v>3.338563017127639e-05</v>
+        <v>3.338563017127643e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02270325150039158</v>
+        <v>0.02270325150039157</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02946682029035674</v>
+        <v>0.02946682029035677</v>
       </c>
       <c r="I6" t="n">
-        <v>2.473719139600489e-07</v>
+        <v>2.473719139600886e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2637072523949958</v>
+        <v>0.2637072523949956</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436998063300782</v>
+        <v>0.00843699806330106</v>
       </c>
     </row>
     <row r="7">
@@ -1879,28 +1655,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2780164956745592</v>
+        <v>0.2780164956745606</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001169644352735124</v>
+        <v>0.0001169644352735129</v>
       </c>
       <c r="F7" t="n">
-        <v>2.696552529413286e-05</v>
+        <v>2.696552529413323e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0200038006148633</v>
+        <v>0.02000380061486338</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01185889686454657</v>
+        <v>0.01185889686454678</v>
       </c>
       <c r="I7" t="n">
-        <v>1.712198186267401e-07</v>
+        <v>1.712198186267404e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2375726985788084</v>
+        <v>0.2375726985788087</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00843699843595469</v>
+        <v>0.008436998435955467</v>
       </c>
     </row>
     <row r="8">
@@ -1918,28 +1694,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3997310305199757</v>
+        <v>0.3997310305199762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001513729640665769</v>
+        <v>0.0001513729640665775</v>
       </c>
       <c r="F8" t="n">
-        <v>4.408832680894804e-05</v>
+        <v>4.408832680894805e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02558334388771563</v>
+        <v>0.02558334388771572</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0678697462377854</v>
+        <v>0.06786974623778538</v>
       </c>
       <c r="I8" t="n">
-        <v>2.684517565177869e-07</v>
+        <v>2.684517565177892e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>0.297645213220756</v>
+        <v>0.2976452132207567</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436997431086557</v>
+        <v>0.008436997431086279</v>
       </c>
     </row>
     <row r="9">
@@ -1957,28 +1733,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2760685626734936</v>
+        <v>0.2760685626734925</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00011586662255097</v>
+        <v>0.0001158666225509694</v>
       </c>
       <c r="F9" t="n">
-        <v>2.620638028380027e-05</v>
+        <v>2.620638028379994e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01997075800041407</v>
+        <v>0.019970758000414</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008005063775580381</v>
+        <v>0.008005063775579985</v>
       </c>
       <c r="I9" t="n">
-        <v>1.909974909628576e-07</v>
+        <v>1.909974909628428e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2395134784314747</v>
+        <v>0.2395134784314744</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436998465698786</v>
+        <v>0.008436998465698398</v>
       </c>
     </row>
     <row r="10">
@@ -1996,28 +1772,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2398354682662817</v>
+        <v>0.2398354682662806</v>
       </c>
       <c r="E10" t="n">
         <v>0.0001058804462370443</v>
       </c>
       <c r="F10" t="n">
-        <v>2.289245783948757e-05</v>
+        <v>2.289245783948758e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.0174575231180247</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004741622281924568</v>
+        <v>0.004741622281924529</v>
       </c>
       <c r="I10" t="n">
-        <v>6.645800221826277e-08</v>
+        <v>6.645800221826241e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2090704847935725</v>
+        <v>0.2090704847935692</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436998710681209</v>
+        <v>0.008436998710683458</v>
       </c>
     </row>
   </sheetData>
@@ -2101,28 +1877,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.780871901432306</v>
+        <v>0.7808719014323059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002329170541490541</v>
+        <v>0.0002329170541490536</v>
       </c>
       <c r="F2" t="n">
-        <v>8.751891389403391e-05</v>
+        <v>8.751891389403393e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03705299165118561</v>
+        <v>0.03705299165118563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2267066103254961</v>
+        <v>0.2267066103254966</v>
       </c>
       <c r="I2" t="n">
-        <v>3.080097898724995e-07</v>
+        <v>3.080097898724961e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5083545610345552</v>
+        <v>0.5083545610345557</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00843699444323609</v>
+        <v>0.00843699444323498</v>
       </c>
     </row>
     <row r="3">
@@ -2140,28 +1916,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5993530736246672</v>
+        <v>0.5993530736246684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001920294371165649</v>
+        <v>0.0001920294371165651</v>
       </c>
       <c r="F3" t="n">
-        <v>6.638292176127781e-05</v>
+        <v>6.638292176127786e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03139512048993765</v>
+        <v>0.03139512048993768</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1487620363269474</v>
+        <v>0.1487620363269481</v>
       </c>
       <c r="I3" t="n">
-        <v>3.174981180363513e-07</v>
+        <v>3.174981180363519e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4105001910708441</v>
+        <v>0.4105001910708452</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436995879942066</v>
+        <v>0.008436995879941511</v>
       </c>
     </row>
     <row r="4">
@@ -2179,28 +1955,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4907676617710626</v>
+        <v>0.4907676617710631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001633145496694449</v>
+        <v>0.0001633145496694451</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117235834304978e-05</v>
+        <v>5.117235834304968e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.02735345615161417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09393620911410068</v>
+        <v>0.09393620911410092</v>
       </c>
       <c r="I4" t="n">
-        <v>3.359957444754823e-07</v>
+        <v>3.359957444755234e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3608261768137392</v>
+        <v>0.360826176813739</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436996787851592</v>
+        <v>0.008436996787852036</v>
       </c>
     </row>
     <row r="5">
@@ -2218,28 +1994,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6213842579365166</v>
+        <v>0.6213842579365165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001863807500215076</v>
+        <v>0.0001863807500215082</v>
       </c>
       <c r="F5" t="n">
-        <v>6.369871684704232e-05</v>
+        <v>6.369871684704234e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03023687992006593</v>
+        <v>0.03023687992006594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1420302928828136</v>
+        <v>0.1420302928828134</v>
       </c>
       <c r="I5" t="n">
-        <v>2.805999448053988e-07</v>
+        <v>2.805999448054026e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4404297292583988</v>
+        <v>0.4404297292583985</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436995808424941</v>
+        <v>0.008436995808425274</v>
       </c>
     </row>
     <row r="6">
@@ -2257,28 +2033,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3936753040916181</v>
+        <v>0.3936753040916179</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001312469477801923</v>
+        <v>0.0001312469477801922</v>
       </c>
       <c r="F6" t="n">
-        <v>3.338563017127639e-05</v>
+        <v>3.338563017127643e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02270325150039158</v>
+        <v>0.02270325150039157</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02946682029035674</v>
+        <v>0.02946682029035677</v>
       </c>
       <c r="I6" t="n">
-        <v>2.473719139600489e-07</v>
+        <v>2.473719139600886e-07</v>
       </c>
       <c r="J6" t="n">
         <v>0.3329033546626491</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436997688355152</v>
+        <v>0.008436997688355041</v>
       </c>
     </row>
     <row r="7">
@@ -2296,28 +2072,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3404802243373144</v>
+        <v>0.3404802243373147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001169644352735124</v>
+        <v>0.0001169644352735129</v>
       </c>
       <c r="F7" t="n">
-        <v>2.696552529413286e-05</v>
+        <v>2.696552529413323e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0200038006148633</v>
+        <v>0.02000380061486338</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01185889686454657</v>
+        <v>0.01185889686454678</v>
       </c>
       <c r="I7" t="n">
-        <v>1.712198186267401e-07</v>
+        <v>1.712198186267404e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3000364275800281</v>
+        <v>0.3000364275800297</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0084369980974901</v>
+        <v>0.008436998097488491</v>
       </c>
     </row>
     <row r="8">
@@ -2335,28 +2111,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4949053532669114</v>
+        <v>0.4949053532669138</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001513729640665769</v>
+        <v>0.0001513729640665775</v>
       </c>
       <c r="F8" t="n">
-        <v>4.408832680894804e-05</v>
+        <v>4.408832680894805e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02558334388771563</v>
+        <v>0.02558334388771572</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0678697462377854</v>
+        <v>0.06786974623778538</v>
       </c>
       <c r="I8" t="n">
-        <v>2.684517565177869e-07</v>
+        <v>2.684517565177892e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3928195364834046</v>
+        <v>0.3928195364834049</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436996915373751</v>
+        <v>0.00843699691537575</v>
       </c>
     </row>
     <row r="9">
@@ -2374,28 +2150,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3471904601764708</v>
+        <v>0.3471904601764692</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00011586662255097</v>
+        <v>0.0001158666225509694</v>
       </c>
       <c r="F9" t="n">
-        <v>2.620638028380027e-05</v>
+        <v>2.620638028379994e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01997075800041407</v>
+        <v>0.019970758000414</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008005063775580381</v>
+        <v>0.008005063775579985</v>
       </c>
       <c r="I9" t="n">
-        <v>1.909974909628576e-07</v>
+        <v>1.909974909628428e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3106353763198341</v>
+        <v>0.3106353763198331</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436998080316449</v>
+        <v>0.008436998080316394</v>
       </c>
     </row>
     <row r="10">
@@ -2413,28 +2189,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3110930700574678</v>
+        <v>0.3110930700574659</v>
       </c>
       <c r="E10" t="n">
         <v>0.0001058804462370443</v>
       </c>
       <c r="F10" t="n">
-        <v>2.289245783948757e-05</v>
+        <v>2.289245783948758e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0.0174575231180247</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004741622281924568</v>
+        <v>0.004741622281924529</v>
       </c>
       <c r="I10" t="n">
-        <v>6.645800221826277e-08</v>
+        <v>6.645800221826241e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2803280869708751</v>
+        <v>0.2803280869708741</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436998324564682</v>
+        <v>0.008436998324563849</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia climate change remind breakdown results.xlsx
+++ b/Results/Ammonia/ammonia climate change remind breakdown results.xlsx
@@ -511,28 +511,28 @@
         <v>2.742852760949717</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2549243901051878</v>
+        <v>0.2549243901051879</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9829935092765117</v>
+        <v>0.9829935092765123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02007413640205909</v>
+        <v>0.0200741364020591</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006604430142347567</v>
+        <v>0.006604430142347578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000580806718677014</v>
+        <v>0.0005808067186768997</v>
       </c>
       <c r="J2" t="n">
-        <v>2.302070441761118e-05</v>
+        <v>2.302070441761124e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04481724723661824</v>
+        <v>0.04481724723661822</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002352325092302141</v>
+        <v>0.0002352325092302142</v>
       </c>
       <c r="M2" t="n">
         <v>1.432599987854667</v>
@@ -553,34 +553,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.725303214842976</v>
+        <v>2.725303214842977</v>
       </c>
       <c r="E3" t="n">
         <v>0.2548473111451526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.979628297876614</v>
+        <v>0.9796282978766134</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01317239671303641</v>
+        <v>0.01317239671303649</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006380735230671422</v>
+        <v>0.006380735230671421</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004430777559259851</v>
+        <v>0.0004430777559264043</v>
       </c>
       <c r="J3" t="n">
-        <v>2.238691079754908e-05</v>
+        <v>2.238691079754906e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03797379953194509</v>
+        <v>0.03797379953194516</v>
       </c>
       <c r="L3" t="n">
         <v>0.0002352214795352527</v>
       </c>
       <c r="M3" t="n">
-        <v>1.432599988199297</v>
+        <v>1.432599988199298</v>
       </c>
     </row>
     <row r="4">
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.717002119291374</v>
+        <v>2.717002119291375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2574557084198207</v>
+        <v>0.2574557084198208</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9786834285538921</v>
+        <v>0.9786834285538926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008317747207024133</v>
+        <v>0.008317747207024127</v>
       </c>
       <c r="H4" t="n">
         <v>0.00625719952265074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003457550814451456</v>
+        <v>0.0003457550814454267</v>
       </c>
       <c r="J4" t="n">
-        <v>2.188573879581109e-05</v>
+        <v>2.188573879581125e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03308522611786629</v>
+        <v>0.03308522611786636</v>
       </c>
       <c r="L4" t="n">
         <v>0.0002351803343958302</v>
@@ -646,31 +646,31 @@
         <v>2.706568639069444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2437895707698048</v>
+        <v>0.2437895707698053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9740429424991267</v>
+        <v>0.9740429424991276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01257632262447243</v>
+        <v>0.01257632262447245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006301838417214081</v>
+        <v>0.006301838417214102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004281652402913289</v>
+        <v>0.0004281652402910837</v>
       </c>
       <c r="J5" t="n">
-        <v>2.188722295844691e-05</v>
+        <v>2.188722295844694e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03657285586542295</v>
+        <v>0.03657285586542313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002350676801236709</v>
+        <v>0.0002350676801236708</v>
       </c>
       <c r="M5" t="n">
-        <v>1.43259998875003</v>
+        <v>1.432599988750028</v>
       </c>
     </row>
     <row r="6">
@@ -691,28 +691,28 @@
         <v>2.670441816574735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2351797720523432</v>
+        <v>0.2351797720523435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9663529060901465</v>
+        <v>0.9663529060901469</v>
       </c>
       <c r="G6" t="n">
         <v>0.002609191540530294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005761063597525462</v>
+        <v>0.005761063597525452</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002229432388318135</v>
+        <v>0.0002229432388311206</v>
       </c>
       <c r="J6" t="n">
-        <v>2.053637100285325e-05</v>
+        <v>2.053637100285328e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02746059603356254</v>
+        <v>0.02746059603356245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00023481804724801</v>
+        <v>0.0002348180472480099</v>
       </c>
       <c r="M6" t="n">
         <v>1.432599989603544</v>
@@ -742,25 +742,25 @@
         <v>0.9641935535072839</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001050066925243466</v>
+        <v>0.001050066925243503</v>
       </c>
       <c r="H7" t="n">
         <v>0.005338925383329605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001753335278144404</v>
+        <v>0.0001753335278147923</v>
       </c>
       <c r="J7" t="n">
-        <v>1.928929448185281e-05</v>
+        <v>1.928929448185286e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02419548969940352</v>
+        <v>0.02419548969940353</v>
       </c>
       <c r="L7" t="n">
         <v>0.0002343822445110979</v>
       </c>
       <c r="M7" t="n">
-        <v>1.432599989849403</v>
+        <v>1.432599989849402</v>
       </c>
     </row>
     <row r="8">
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.674253781160294</v>
+        <v>2.674253781160293</v>
       </c>
       <c r="E8" t="n">
         <v>0.2304107916572901</v>
       </c>
       <c r="F8" t="n">
-        <v>0.967758829591565</v>
+        <v>0.967758829591558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006009646307155857</v>
+        <v>0.006009646307155851</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005977601838386653</v>
+        <v>0.00597760183838666</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002965216232766402</v>
+        <v>0.0002965216232764366</v>
       </c>
       <c r="J8" t="n">
-        <v>2.120614075920208e-05</v>
+        <v>2.120614075920196e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03094419632695144</v>
+        <v>0.03094419632695138</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002349980674677673</v>
+        <v>0.0002349980674677672</v>
       </c>
       <c r="M8" t="n">
-        <v>1.432599989607441</v>
+        <v>1.432599989607448</v>
       </c>
     </row>
     <row r="9">
@@ -823,34 +823,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.624396549169136</v>
+        <v>2.624396549169135</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2078418660809996</v>
+        <v>0.2078418660809997</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9532771809726606</v>
+        <v>0.9532771809726609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0007088224816535315</v>
+        <v>0.000708822481653544</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005389317962532587</v>
+        <v>0.005389317962532599</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000169804045387021</v>
+        <v>0.00016980404538704</v>
       </c>
       <c r="J9" t="n">
-        <v>1.95516540948669e-05</v>
+        <v>1.955165409486694e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02415552318239289</v>
+        <v>0.02415552318239297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002344918326662287</v>
+        <v>0.0002344918326662288</v>
       </c>
       <c r="M9" t="n">
-        <v>1.432599990956749</v>
+        <v>1.432599990956747</v>
       </c>
     </row>
     <row r="10">
@@ -874,28 +874,28 @@
         <v>0.2058297930324351</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9303570490019334</v>
+        <v>0.9303570490019338</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004198553024886839</v>
+        <v>0.0004198553024886959</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004906348575617324</v>
+        <v>0.004906348575617325</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001385799366023206</v>
+        <v>0.000138579936602131</v>
       </c>
       <c r="J10" t="n">
-        <v>1.788546422498255e-05</v>
+        <v>1.788546422498254e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02111565341565224</v>
+        <v>0.02111565341565225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002338649298330928</v>
+        <v>0.000233864929833093</v>
       </c>
       <c r="M10" t="n">
-        <v>1.432599991612834</v>
+        <v>1.432599991612833</v>
       </c>
     </row>
   </sheetData>
@@ -989,31 +989,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.990557743927718</v>
+        <v>1.990557743927719</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2549243901051878</v>
+        <v>0.2549243901051879</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3743660563077815</v>
+        <v>0.3743660563077816</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02007413640205909</v>
+        <v>0.0200741364020591</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006604430142347567</v>
+        <v>0.006604430142347578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000580806718677014</v>
+        <v>0.0005808067186768997</v>
       </c>
       <c r="J2" t="n">
-        <v>2.302070441761118e-05</v>
+        <v>2.302070441761124e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04481724723661824</v>
+        <v>0.04481724723661822</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002352325092302141</v>
+        <v>0.0002352325092302142</v>
       </c>
       <c r="M2" t="n">
         <v>1.288932423801399</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.933852614785587</v>
+        <v>1.933852614785586</v>
       </c>
       <c r="E3" t="n">
         <v>0.2548473111451526</v>
@@ -1043,25 +1043,25 @@
         <v>0.331845260930385</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01317239671303641</v>
+        <v>0.01317239671303649</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006380735230671422</v>
+        <v>0.006380735230671421</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004430777559259851</v>
+        <v>0.0004430777559264043</v>
       </c>
       <c r="J3" t="n">
-        <v>2.238691079754908e-05</v>
+        <v>2.238691079754906e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03797379953194509</v>
+        <v>0.03797379953194516</v>
       </c>
       <c r="L3" t="n">
         <v>0.0002352214795352527</v>
       </c>
       <c r="M3" t="n">
-        <v>1.288932425088137</v>
+        <v>1.288932425088136</v>
       </c>
     </row>
     <row r="4">
@@ -1079,28 +1079,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.898315518402883</v>
+        <v>1.898315518402884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2574557084198207</v>
+        <v>0.2574557084198208</v>
       </c>
       <c r="F4" t="n">
         <v>0.3036643901212501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008317747207024133</v>
+        <v>0.008317747207024127</v>
       </c>
       <c r="H4" t="n">
         <v>0.00625719952265074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003457550814451456</v>
+        <v>0.0003457550814454267</v>
       </c>
       <c r="J4" t="n">
-        <v>2.188573879581109e-05</v>
+        <v>2.188573879581125e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03308522611786629</v>
+        <v>0.03308522611786636</v>
       </c>
       <c r="L4" t="n">
         <v>0.0002351803343958302</v>
@@ -1127,31 +1127,31 @@
         <v>1.909829097870338</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2437895707698048</v>
+        <v>0.2437895707698053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3209709642839296</v>
+        <v>0.32097096428393</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01257632262447243</v>
+        <v>0.01257632262447245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006301838417214081</v>
+        <v>0.006301838417214102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004281652402913289</v>
+        <v>0.0004281652402910837</v>
       </c>
       <c r="J5" t="n">
-        <v>2.188722295844691e-05</v>
+        <v>2.188722295844694e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03657285586542295</v>
+        <v>0.03657285586542313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002350676801236709</v>
+        <v>0.0002350676801236708</v>
       </c>
       <c r="M5" t="n">
-        <v>1.288932425766121</v>
+        <v>1.28893242576612</v>
       </c>
     </row>
     <row r="6">
@@ -1172,31 +1172,31 @@
         <v>1.814452288503936</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2351797720523432</v>
+        <v>0.2351797720523435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2540309395776655</v>
+        <v>0.2540309395776656</v>
       </c>
       <c r="G6" t="n">
         <v>0.002609191540530294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005761063597525462</v>
+        <v>0.005761063597525452</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002229432388318135</v>
+        <v>0.0002229432388311206</v>
       </c>
       <c r="J6" t="n">
-        <v>2.053637100285325e-05</v>
+        <v>2.053637100285328e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02746059603356254</v>
+        <v>0.02746059603356245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00023481804724801</v>
+        <v>0.0002348180472480099</v>
       </c>
       <c r="M6" t="n">
-        <v>1.288932428045226</v>
+        <v>1.288932428045227</v>
       </c>
     </row>
     <row r="7">
@@ -1220,22 +1220,22 @@
         <v>0.2317174579778651</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2421366373816277</v>
+        <v>0.2421366373816278</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001050066925243466</v>
+        <v>0.001050066925243503</v>
       </c>
       <c r="H7" t="n">
         <v>0.005338925383329605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001753335278144404</v>
+        <v>0.0001753335278147923</v>
       </c>
       <c r="J7" t="n">
-        <v>1.928929448185281e-05</v>
+        <v>1.928929448185286e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02419548969940352</v>
+        <v>0.02419548969940353</v>
       </c>
       <c r="L7" t="n">
         <v>0.0002343822445110979</v>
@@ -1259,34 +1259,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.834692530302356</v>
+        <v>1.834692530302357</v>
       </c>
       <c r="E8" t="n">
         <v>0.2304107916572901</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2718651406872118</v>
+        <v>0.2718651406872117</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006009646307155857</v>
+        <v>0.006009646307155851</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005977601838386653</v>
+        <v>0.00597760183838666</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002965216232766402</v>
+        <v>0.0002965216232764366</v>
       </c>
       <c r="J8" t="n">
-        <v>2.120614075920208e-05</v>
+        <v>2.120614075920196e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03094419632695144</v>
+        <v>0.03094419632695138</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002349980674677673</v>
+        <v>0.0002349980674677672</v>
       </c>
       <c r="M8" t="n">
-        <v>1.288932427653857</v>
+        <v>1.288932427653858</v>
       </c>
     </row>
     <row r="9">
@@ -1307,31 +1307,31 @@
         <v>1.751954677230468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2078418660809996</v>
+        <v>0.2078418660809997</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2245028701964585</v>
+        <v>0.224502870196459</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0007088224816535315</v>
+        <v>0.000708822481653544</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005389317962532587</v>
+        <v>0.005389317962532599</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000169804045387021</v>
+        <v>0.00016980404538704</v>
       </c>
       <c r="J9" t="n">
-        <v>1.95516540948669e-05</v>
+        <v>1.955165409486694e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02415552318239289</v>
+        <v>0.02415552318239297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002344918326662287</v>
+        <v>0.0002344918326662288</v>
       </c>
       <c r="M9" t="n">
-        <v>1.288932429794283</v>
+        <v>1.288932429794282</v>
       </c>
     </row>
     <row r="10">
@@ -1355,25 +1355,25 @@
         <v>0.2058297930324351</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2213413332729941</v>
+        <v>0.2213413332729942</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004198553024886839</v>
+        <v>0.0004198553024886959</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004906348575617324</v>
+        <v>0.004906348575617325</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001385799366023206</v>
+        <v>0.000138579936602131</v>
       </c>
       <c r="J10" t="n">
-        <v>1.788546422498255e-05</v>
+        <v>1.788546422498254e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02111565341565224</v>
+        <v>0.02111565341565225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002338649298330928</v>
+        <v>0.000233864929833093</v>
       </c>
       <c r="M10" t="n">
         <v>1.288932429974965</v>
@@ -1460,28 +1460,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6340057313660551</v>
+        <v>0.6340057313660546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002329170541490536</v>
+        <v>0.0002329170541490539</v>
       </c>
       <c r="F2" t="n">
-        <v>8.751891389403393e-05</v>
+        <v>8.7518913894034e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03705299165118563</v>
+        <v>0.0370529916511856</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2267066103254966</v>
+        <v>0.2267066103254969</v>
       </c>
       <c r="I2" t="n">
-        <v>3.080097898724961e-07</v>
+        <v>3.08009789872481e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3614883901724956</v>
+        <v>0.3614883901724943</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436995239044287</v>
+        <v>0.008436995239044842</v>
       </c>
     </row>
     <row r="3">
@@ -1499,28 +1499,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5073965993184059</v>
+        <v>0.5073965993184061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001920294371165651</v>
+        <v>0.0001920294371165647</v>
       </c>
       <c r="F3" t="n">
-        <v>6.638292176127786e-05</v>
+        <v>6.638292176127778e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03139512048993768</v>
+        <v>0.03139512048993767</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1487620363269481</v>
+        <v>0.1487620363269473</v>
       </c>
       <c r="I3" t="n">
-        <v>3.174981180363519e-07</v>
+        <v>3.174981180362162e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3185437162663073</v>
+        <v>0.3185437162663063</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436996378216877</v>
+        <v>0.00843699637821882</v>
       </c>
     </row>
     <row r="4">
@@ -1538,28 +1538,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4288648735213333</v>
+        <v>0.428864873521334</v>
       </c>
       <c r="E4" t="n">
         <v>0.0001633145496694451</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117235834304968e-05</v>
+        <v>5.117235834304972e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02735345615161417</v>
+        <v>0.02735345615161422</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09393620911410092</v>
+        <v>0.09393620911410082</v>
       </c>
       <c r="I4" t="n">
-        <v>3.359957444755234e-07</v>
+        <v>3.359957444754829e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2989233882285833</v>
+        <v>0.298923388228583</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436997123277945</v>
+        <v>0.008436997123278944</v>
       </c>
     </row>
     <row r="5">
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5043918025945243</v>
+        <v>0.5043918025945258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001863807500215082</v>
+        <v>0.0001863807500215085</v>
       </c>
       <c r="F5" t="n">
-        <v>6.369871684704234e-05</v>
+        <v>6.369871684704246e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03023687992006594</v>
+        <v>0.03023687992006605</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1420302928828134</v>
+        <v>0.1420302928828136</v>
       </c>
       <c r="I5" t="n">
-        <v>2.805999448054026e-07</v>
+        <v>2.805999448054037e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3234372732824713</v>
+        <v>0.3234372732824722</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436996442360289</v>
+        <v>0.008436996442360511</v>
       </c>
     </row>
     <row r="6">
@@ -1616,28 +1616,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3244792021989104</v>
+        <v>0.3244792021989101</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001312469477801922</v>
+        <v>0.0001312469477801923</v>
       </c>
       <c r="F6" t="n">
-        <v>3.338563017127643e-05</v>
+        <v>3.338563017127634e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02270325150039157</v>
+        <v>0.02270325150039151</v>
       </c>
       <c r="H6" t="n">
         <v>0.02946682029035677</v>
       </c>
       <c r="I6" t="n">
-        <v>2.473719139600886e-07</v>
+        <v>2.473719139600509e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2637072523949956</v>
+        <v>0.2637072523949949</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00843699806330106</v>
+        <v>0.008436998063301504</v>
       </c>
     </row>
     <row r="7">
@@ -1655,28 +1655,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2780164956745606</v>
+        <v>0.2780164956745603</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001169644352735129</v>
       </c>
       <c r="F7" t="n">
-        <v>2.696552529413323e-05</v>
+        <v>2.696552529413351e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02000380061486338</v>
+        <v>0.02000380061486334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01185889686454678</v>
+        <v>0.01185889686454629</v>
       </c>
       <c r="I7" t="n">
-        <v>1.712198186267404e-07</v>
+        <v>1.712198186267406e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2375726985788087</v>
+        <v>0.2375726985788083</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998435955467</v>
+        <v>0.008436998435956189</v>
       </c>
     </row>
     <row r="8">
@@ -1694,28 +1694,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3997310305199762</v>
+        <v>0.3997310305199759</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001513729640665775</v>
+        <v>0.0001513729640665771</v>
       </c>
       <c r="F8" t="n">
-        <v>4.408832680894805e-05</v>
+        <v>4.408832680894798e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02558334388771572</v>
+        <v>0.02558334388771566</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06786974623778538</v>
+        <v>0.06786974623778542</v>
       </c>
       <c r="I8" t="n">
-        <v>2.684517565177892e-07</v>
+        <v>2.684517565177877e-07</v>
       </c>
       <c r="J8" t="n">
         <v>0.2976452132207567</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436997431086279</v>
+        <v>0.008436997431086057</v>
       </c>
     </row>
     <row r="9">
@@ -1733,28 +1733,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2760685626734925</v>
+        <v>0.276068562673492</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001158666225509694</v>
+        <v>0.0001158666225509697</v>
       </c>
       <c r="F9" t="n">
-        <v>2.620638028379994e-05</v>
+        <v>2.620638028380019e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.019970758000414</v>
+        <v>0.01997075800041405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008005063775579985</v>
+        <v>0.008005063775580332</v>
       </c>
       <c r="I9" t="n">
-        <v>1.909974909628428e-07</v>
+        <v>1.909974909628568e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2395134784314744</v>
+        <v>0.239513478431475</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436998465698398</v>
+        <v>0.008436998465696899</v>
       </c>
     </row>
     <row r="10">
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2398354682662806</v>
+        <v>0.2398354682662816</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001058804462370443</v>
+        <v>0.0001058804462370445</v>
       </c>
       <c r="F10" t="n">
-        <v>2.289245783948758e-05</v>
+        <v>2.289245783948765e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0174575231180247</v>
+        <v>0.01745752311802472</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004741622281924529</v>
+        <v>0.004741622281924611</v>
       </c>
       <c r="I10" t="n">
-        <v>6.645800221826241e-08</v>
+        <v>6.645800221827002e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2090704847935692</v>
+        <v>0.2090704847935721</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436998710683458</v>
+        <v>0.008436998710681459</v>
       </c>
     </row>
   </sheetData>
@@ -1877,28 +1877,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7808719014323059</v>
+        <v>0.780871901432307</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002329170541490536</v>
+        <v>0.0002329170541490539</v>
       </c>
       <c r="F2" t="n">
-        <v>8.751891389403393e-05</v>
+        <v>8.7518913894034e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03705299165118563</v>
+        <v>0.0370529916511856</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2267066103254966</v>
+        <v>0.2267066103254969</v>
       </c>
       <c r="I2" t="n">
-        <v>3.080097898724961e-07</v>
+        <v>3.08009789872481e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5083545610345557</v>
+        <v>0.5083545610345561</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00843699444323498</v>
+        <v>0.008436994443235313</v>
       </c>
     </row>
     <row r="3">
@@ -1916,28 +1916,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5993530736246684</v>
+        <v>0.5993530736246677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001920294371165651</v>
+        <v>0.0001920294371165647</v>
       </c>
       <c r="F3" t="n">
-        <v>6.638292176127786e-05</v>
+        <v>6.638292176127778e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03139512048993768</v>
+        <v>0.03139512048993767</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1487620363269481</v>
+        <v>0.1487620363269473</v>
       </c>
       <c r="I3" t="n">
-        <v>3.174981180363519e-07</v>
+        <v>3.174981180362162e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4105001910708452</v>
+        <v>0.4105001910708445</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436995879941511</v>
+        <v>0.008436995879942288</v>
       </c>
     </row>
     <row r="4">
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4907676617710631</v>
+        <v>0.490767661771063</v>
       </c>
       <c r="E4" t="n">
         <v>0.0001633145496694451</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117235834304968e-05</v>
+        <v>5.117235834304972e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02735345615161417</v>
+        <v>0.02735345615161422</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09393620911410092</v>
+        <v>0.09393620911410082</v>
       </c>
       <c r="I4" t="n">
-        <v>3.359957444755234e-07</v>
+        <v>3.359957444754829e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.360826176813739</v>
+        <v>0.3608261768137395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436996787852036</v>
+        <v>0.008436996787851481</v>
       </c>
     </row>
     <row r="5">
@@ -1994,28 +1994,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6213842579365165</v>
+        <v>0.6213842579365181</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001863807500215082</v>
+        <v>0.0001863807500215085</v>
       </c>
       <c r="F5" t="n">
-        <v>6.369871684704234e-05</v>
+        <v>6.369871684704246e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03023687992006594</v>
+        <v>0.03023687992006605</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1420302928828134</v>
+        <v>0.1420302928828136</v>
       </c>
       <c r="I5" t="n">
-        <v>2.805999448054026e-07</v>
+        <v>2.805999448054037e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4404297292583985</v>
+        <v>0.4404297292584001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436995808425274</v>
+        <v>0.008436995808424941</v>
       </c>
     </row>
     <row r="6">
@@ -2033,28 +2033,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3936753040916179</v>
+        <v>0.3936753040916177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001312469477801922</v>
+        <v>0.0001312469477801923</v>
       </c>
       <c r="F6" t="n">
-        <v>3.338563017127643e-05</v>
+        <v>3.338563017127634e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02270325150039157</v>
+        <v>0.02270325150039151</v>
       </c>
       <c r="H6" t="n">
         <v>0.02946682029035677</v>
       </c>
       <c r="I6" t="n">
-        <v>2.473719139600886e-07</v>
+        <v>2.473719139600509e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3329033546626491</v>
+        <v>0.3329033546626496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436997688355041</v>
+        <v>0.008436997688354431</v>
       </c>
     </row>
     <row r="7">
@@ -2072,28 +2072,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3404802243373147</v>
+        <v>0.3404802243373136</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001169644352735129</v>
       </c>
       <c r="F7" t="n">
-        <v>2.696552529413323e-05</v>
+        <v>2.696552529413351e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02000380061486338</v>
+        <v>0.02000380061486334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01185889686454678</v>
+        <v>0.01185889686454629</v>
       </c>
       <c r="I7" t="n">
-        <v>1.712198186267404e-07</v>
+        <v>1.712198186267406e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3000364275800297</v>
+        <v>0.3000364275800278</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998097488491</v>
+        <v>0.008436998097489934</v>
       </c>
     </row>
     <row r="8">
@@ -2111,28 +2111,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4949053532669138</v>
+        <v>0.4949053532669124</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001513729640665775</v>
+        <v>0.0001513729640665771</v>
       </c>
       <c r="F8" t="n">
-        <v>4.408832680894805e-05</v>
+        <v>4.408832680894798e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02558334388771572</v>
+        <v>0.02558334388771566</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06786974623778538</v>
+        <v>0.06786974623778542</v>
       </c>
       <c r="I8" t="n">
-        <v>2.684517565177892e-07</v>
+        <v>2.684517565177877e-07</v>
       </c>
       <c r="J8" t="n">
         <v>0.3928195364834049</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00843699691537575</v>
+        <v>0.008436996915374362</v>
       </c>
     </row>
     <row r="9">
@@ -2150,28 +2150,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3471904601764692</v>
+        <v>0.3471904601764706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001158666225509694</v>
+        <v>0.0001158666225509697</v>
       </c>
       <c r="F9" t="n">
-        <v>2.620638028379994e-05</v>
+        <v>2.620638028380019e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.019970758000414</v>
+        <v>0.01997075800041405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008005063775579985</v>
+        <v>0.008005063775580332</v>
       </c>
       <c r="I9" t="n">
-        <v>1.909974909628428e-07</v>
+        <v>1.909974909628568e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3106353763198331</v>
+        <v>0.310635376319834</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436998080316394</v>
+        <v>0.008436998080316505</v>
       </c>
     </row>
     <row r="10">
@@ -2189,28 +2189,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3110930700574659</v>
+        <v>0.3110930700574679</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001058804462370443</v>
+        <v>0.0001058804462370445</v>
       </c>
       <c r="F10" t="n">
-        <v>2.289245783948758e-05</v>
+        <v>2.289245783948765e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0174575231180247</v>
+        <v>0.01745752311802472</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004741622281924529</v>
+        <v>0.004741622281924611</v>
       </c>
       <c r="I10" t="n">
-        <v>6.645800221826241e-08</v>
+        <v>6.645800221827002e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2803280869708741</v>
+        <v>0.2803280869708753</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436998324563849</v>
+        <v>0.008436998324564571</v>
       </c>
     </row>
   </sheetData>
